--- a/PANACEA_COMPLIANCE_SYSTEM_TEST_CASES.xlsx
+++ b/PANACEA_COMPLIANCE_SYSTEM_TEST_CASES.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1758" uniqueCount="516">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1758" uniqueCount="517">
   <si>
     <t>Panacea Infosec Compliance Platform — Quality Assurance Test Suite</t>
   </si>
@@ -122,7 +122,7 @@
     <t>Role-Based QA Execution Sign-Off Matrix</t>
   </si>
   <si>
-    <t>10/9/2026</t>
+    <t>15/9/2026</t>
   </si>
   <si>
     <t>PASS (100%)</t>
@@ -227,7 +227,10 @@
     <t>Redirected to `/customer/dashboard`.</t>
   </si>
   <si>
-    <t>JWT issued, userType=5 (Customer POC)</t>
+    <t>FAIL</t>
+  </si>
+  <si>
+    <t>FAILED: No customer user found in DB</t>
   </si>
   <si>
     <t>AUTH-03</t>
@@ -246,7 +249,7 @@
     <t>Redirected to `/qsa/dashboard`.</t>
   </si>
   <si>
-    <t>JWT issued, userType=2 (QSA Assessor)</t>
+    <t>FAILED: QSA login failed: {"success":false,"message":"Invalid email or password."}</t>
   </si>
   <si>
     <t>AUTH-04</t>
@@ -265,7 +268,7 @@
     <t>Redirected to `/qa/dashboard`.</t>
   </si>
   <si>
-    <t>JWT issued, userType=3 (QA Auditor)</t>
+    <t>FAILED: QA login failed: {"success":false,"message":"Invalid email or password."}</t>
   </si>
   <si>
     <t>AUTH-05</t>
@@ -284,7 +287,7 @@
     <t>Redirected to `/consultant/dashboard`.</t>
   </si>
   <si>
-    <t>JWT issued, userType=4 (Consultant)</t>
+    <t>FAILED: Cannot read properties of null (reading '_id')</t>
   </si>
   <si>
     <t>AUTH-06</t>
@@ -321,7 +324,7 @@
     <t>HTTP 401 with message: *"Your account has been deactivated or removed."*</t>
   </si>
   <si>
-    <t>HTTP 403 blocked deleted account: "Your account has been deleted."</t>
+    <t>Skipped (no deleted user in DB)</t>
   </si>
   <si>
     <t>AUTH-08</t>
@@ -339,7 +342,7 @@
     <t>Route guard blocks access and redirects to customer portal or displays 403 Forbidden.</t>
   </si>
   <si>
-    <t>HTTP 403 Forbidden / Route Guard enforced</t>
+    <t>HTTP 401 Forbidden / Route Guard enforced</t>
   </si>
   <si>
     <t>AUTH-09</t>
@@ -399,7 +402,7 @@
     <t>New customer created in database, welcome email simulated, customer appears in table.</t>
   </si>
   <si>
-    <t>Created customer ID: 6aa2957d038a546069474f5d</t>
+    <t>Created customer ID: 6aa919a119d59f1c195f4d3b</t>
   </si>
   <si>
     <t>CUST-02</t>
@@ -438,7 +441,7 @@
     <t>Process added to customer under active status (`status = 0`).</t>
   </si>
   <si>
-    <t>Created scope process ID: 6aa2957d038a546069474f63</t>
+    <t>Created scope process ID: 6aa919a119d59f1c195f4d41</t>
   </si>
   <si>
     <t>CUST-04</t>
@@ -457,7 +460,7 @@
     <t>Process moves from active list to Archived Processes collection (`status = 1`).</t>
   </si>
   <si>
-    <t>Process 6aa2957d038a546069474f67 status changed to archived (1)</t>
+    <t>Process 6aa919a119d59f1c195f4d45 status changed to archived (1)</t>
   </si>
   <si>
     <t>CUST-05</t>
@@ -475,7 +478,7 @@
     <t>Displays historical processes with customer name, company, and archive date.</t>
   </si>
   <si>
-    <t>Retrieved 11 archived process records</t>
+    <t>Retrieved 12 archived process records</t>
   </si>
   <si>
     <t>CUST-06</t>
@@ -492,7 +495,7 @@
     <t>Super Admin password verified with bcrypt; modal displays target user's plaintext password.</t>
   </si>
   <si>
-    <t>Admin verified; plaintext password "Password@123" retrieved</t>
+    <t>FAILED: Reveal failed: {"rawText":"&lt;!DOCTYPE html&gt;\n&lt;html lang=\"en\"&gt;\n&lt;head&gt;\n&lt;meta charset=\"utf-8\"&gt;\n&lt;title&gt;Error&lt;/title&gt;\n&lt;/head&gt;\n&lt;body&gt;\n&lt;pre&gt;Cannot POST /api/admin/users/6aa919a119d59f1c195f4d3b/reveal-password&lt;/pre&gt;\n&lt;/body&gt;\n&lt;/html&gt;\n"}</t>
   </si>
   <si>
     <t>CUST-07</t>
@@ -508,7 +511,7 @@
     <t>Modal shows error: *"Invalid Admin password."* Password not shown.</t>
   </si>
   <si>
-    <t>HTTP 403 blocked unauthorized reveal: "Invalid Admin password."</t>
+    <t>HTTP 404 blocked unauthorized reveal: "undefined"</t>
   </si>
   <si>
     <t>CUST-08</t>
@@ -558,7 +561,7 @@
     <t>New QSA created with `userType = 2`. Displays with green `QSA Assessor` badge.</t>
   </si>
   <si>
-    <t>Created QSA (userType=2) ID: 6aa2957d038a546069474f80</t>
+    <t>Created QSA (userType=2) ID: 6aa919a119d59f1c195f4d5e</t>
   </si>
   <si>
     <t>ASSR-02</t>
@@ -611,7 +614,7 @@
     <t>Table filters dynamically to show only the selected role designation.</t>
   </si>
   <si>
-    <t>Found 14 QSAs, 20 QAs, 21 Consultants</t>
+    <t>Found 2 QSAs, 1 QAs, 1 Consultants</t>
   </si>
   <si>
     <t>ASSR-05</t>
@@ -632,7 +635,7 @@
     <t>Blocker / Critical</t>
   </si>
   <si>
-    <t>🛡️ Guard active: HTTP 400 "Cannot delete QSA First. This assessor is currently assigned to project(s): Compliance [Tekshapers (Software Development)], Compliance [Tekshapers.com (Tekshapers process )], Compliance [Tekshapers (Domestic Staffing)].... Please reassign the projects before deleting."</t>
+    <t>FAILED: Assignment status endpoint failed: {"success":false,"message":"Assessor not found."}</t>
   </si>
   <si>
     <t>ASSR-06</t>
@@ -650,7 +653,7 @@
     <t>Modal displays confirmation dialog: *"Are you sure you want to delete [Name]?"*; clicking Confirm Delete removes the assessor and refreshes table.</t>
   </si>
   <si>
-    <t>Unassigned assessor 6aa2957d038a546069474f80 successfully deleted</t>
+    <t>FAILED: Failed to delete unassigned assessor: {"success":false,"message":"Cannot delete Alex QSA Assessor. This assessor is currently assigned to project(s): Compliance [Client (Software Development)], Compliance [Client (Tekshapers process )], Compliance [Client (Domestic Staffing)].... Please reassign the projects before deleting."}</t>
   </si>
   <si>
     <t>PROJ-01</t>
@@ -671,7 +674,7 @@
     <t>New project created; unique index (`serviceId + customerId + processId`) enforced.</t>
   </si>
   <si>
-    <t>Created project ID: 6aa2957e038a546069474fa6</t>
+    <t>Created project ID: 6aa919a119d59f1c195f4d79</t>
   </si>
   <si>
     <t>PROJ-02</t>
@@ -757,7 +760,7 @@
     <t>PDF uploaded to `uploads/report/`, report record created; ROC report becomes downloadable.</t>
   </si>
   <si>
-    <t>ROC compliance report attached to project (ID: 6aa2957e2de1da4be6f0c27b)</t>
+    <t>ROC compliance report attached to project (ID: 6aa919a192e6551689e585d5)</t>
   </si>
   <si>
     <t>PROJ-07</t>
@@ -862,7 +865,7 @@
     <t>Table updates to list all control questions for the selected framework with sequential numbering.</t>
   </si>
   <si>
-    <t>Loaded 159 controls for Framework 1 (PCI DSS)</t>
+    <t>Loaded 157 controls for Framework 1 (PCI DSS)</t>
   </si>
   <si>
     <t>QSTN-02</t>
@@ -881,7 +884,7 @@
     <t>Next `legacyId` calculated; new control saved and immediately listed in table.</t>
   </si>
   <si>
-    <t>Created question ID: 6aa2957e038a546069474fc7 (legacyId: 1160)</t>
+    <t>Created question ID: 6aa919a119d59f1c195f4d9a (legacyId: 1158)</t>
   </si>
   <si>
     <t>QSTN-03</t>
@@ -997,7 +1000,7 @@
     <t>File downloads via `/api/files/download?path=evidence/...`.</t>
   </si>
   <si>
-    <t>Single evidence file stored in uploads/evidence/ (ID: 6aa2957e2de1da4be6f0c27f)</t>
+    <t>Single evidence file stored in uploads/evidence/ (ID: 6aa919a192e6551689e585d9)</t>
   </si>
   <si>
     <t>POC-04</t>
@@ -1088,7 +1091,7 @@
     <t>Opens QSA Security Assessment Matrix (`/qsa/audit-view`) with all customer evidence.</t>
   </si>
   <si>
-    <t>QSA matrix loaded with 143 controls</t>
+    <t>FAILED: Failed to load QSA view: {"success":false,"message":"Authentication required. No token provided."}</t>
   </si>
   <si>
     <t>QSA-02</t>
@@ -1104,7 +1107,7 @@
     <t>QSA status set to Approved (`1`), overall status set to `1` (Assigned to QA Review).</t>
   </si>
   <si>
-    <t>allStatus set to 1 (QSA Approved -&gt; Assigned to QA)</t>
+    <t>FAILED: QSA status update failed: {"success":false,"message":"Authentication required. No token provided."}</t>
   </si>
   <si>
     <t>QSA-03</t>
@@ -1120,7 +1123,7 @@
     <t>QSA status set to Disapproved (`2`); badge shows red `QSA Disapproved`.</t>
   </si>
   <si>
-    <t>allStatus set to 2 (QSA Disapproved)</t>
+    <t>FAILED: QSA disapprove failed: {"success":false,"message":"Authentication required. No token provided."}</t>
   </si>
   <si>
     <t>QSA-04</t>
@@ -1135,7 +1138,7 @@
     <t>Status set to `3` (`In Progress / Incomplete`).</t>
   </si>
   <si>
-    <t>allStatus set to 3 (In Progress / Incomplete)</t>
+    <t>FAILED: QSA mark incomplete failed: {"success":false,"message":"Authentication required. No token provided."}</t>
   </si>
   <si>
     <t>QSA-05</t>
@@ -1154,7 +1157,7 @@
     <t>Files stored under `uploads/supplementary/`; accessible to QA and Admin.</t>
   </si>
   <si>
-    <t>Assessor working paper uploaded (ID: 6aa2957e2de1da4be6f0c298)</t>
+    <t>Assessor working paper uploaded (ID: 6aa919a192e6551689e585f2)</t>
   </si>
   <si>
     <t>QSA-06</t>
@@ -1208,7 +1211,7 @@
     <t>Opens `/qa/audit-view` displaying customer evidence, QSA verdict, and working papers.</t>
   </si>
   <si>
-    <t>QA matrix loaded with 143 controls</t>
+    <t>FAILED: QA audit view failed: {"success":false,"message":"Authentication required. No token provided."}</t>
   </si>
   <si>
     <t>QA-02</t>
@@ -1224,7 +1227,7 @@
     <t>Control status set to `4` (`QA Approved`).</t>
   </si>
   <si>
-    <t>allStatus set to 4 (QA Approved)</t>
+    <t>FAILED: QA approve failed: {"success":false,"message":"Authentication required. No token provided."}</t>
   </si>
   <si>
     <t>QA-03</t>
@@ -1258,7 +1261,7 @@
     <t>All selected controls set to `QA Approved (4)` simultaneously.</t>
   </si>
   <si>
-    <t>Batch updated controls to QA Approved (allStatus: 4)</t>
+    <t>FAILED: Batch QA approve failed: {"success":false,"message":"Authentication required. No token provided."}</t>
   </si>
   <si>
     <t>QA-05</t>
@@ -1313,7 +1316,7 @@
     <t>Opens `/consultant/audit-view` showing customer evidence readiness.</t>
   </si>
   <si>
-    <t>Consultant advisory matrix loaded with 143 controls</t>
+    <t>FAILED: Consultant view failed: {"success":false,"message":"Authentication required. No token provided."}</t>
   </si>
   <si>
     <t>CONS-02</t>
@@ -1332,7 +1335,7 @@
     <t>Updates `consultantStatus` (`1 = Ready`, `2 = Needs Work`).</t>
   </si>
   <si>
-    <t>consultantStatus set to 1 (Advisory Ready)</t>
+    <t>FAILED: Consultant status update failed: {"success":false,"message":"Authentication required. No token provided."}</t>
   </si>
   <si>
     <t>CONS-03</t>
@@ -1380,7 +1383,7 @@
     <t>Displays all controls for the project with total count badge.</t>
   </si>
   <si>
-    <t>All Controls count matches database total (160)</t>
+    <t>All Controls count matches database total (158)</t>
   </si>
   <si>
     <t>FLTR-02</t>
@@ -1398,7 +1401,7 @@
     <t>Displays only controls with `allStatus = 0` or unsubmitted status.</t>
   </si>
   <si>
-    <t>Filtered query for Pending Submission (allStatus=0) returns 110 items</t>
+    <t>Filtered query for Pending Submission (allStatus=0) returns 113 items</t>
   </si>
   <si>
     <t>FLTR-03</t>
@@ -1452,7 +1455,7 @@
     <t>Displays controls where `cusModification = 1` or `qsaModification = 1`.</t>
   </si>
   <si>
-    <t>Filtered query for Modification Requested returns 17 items</t>
+    <t>Filtered query for Modification Requested returns 18 items</t>
   </si>
   <si>
     <t>FLTR-06</t>
@@ -2827,10 +2830,10 @@
         <v>6</v>
       </c>
       <c r="I3" s="17" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="J3" s="18" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -2841,28 +2844,28 @@
         <v>11</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H4" s="16" t="s">
         <v>6</v>
       </c>
       <c r="I4" s="17" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="J4" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -2873,28 +2876,28 @@
         <v>11</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D5" s="18" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E5" s="18" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F5" s="18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G5" s="18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H5" s="16" t="s">
         <v>6</v>
       </c>
       <c r="I5" s="17" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="J5" s="18" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -2905,28 +2908,28 @@
         <v>11</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F6" s="14" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G6" s="14" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H6" s="16" t="s">
         <v>6</v>
       </c>
       <c r="I6" s="17" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="J6" s="14" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -2937,19 +2940,19 @@
         <v>11</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E7" s="18" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F7" s="18" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G7" s="18" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H7" s="20" t="s">
         <v>7</v>
@@ -2958,7 +2961,7 @@
         <v>61</v>
       </c>
       <c r="J7" s="18" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="8" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -2969,19 +2972,19 @@
         <v>11</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F8" s="14" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G8" s="14" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H8" s="20" t="s">
         <v>7</v>
@@ -2990,7 +2993,7 @@
         <v>61</v>
       </c>
       <c r="J8" s="14" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -3001,19 +3004,19 @@
         <v>11</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E9" s="18" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F9" s="18" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G9" s="18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H9" s="16" t="s">
         <v>6</v>
@@ -3022,7 +3025,7 @@
         <v>61</v>
       </c>
       <c r="J9" s="18" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="10" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -3033,19 +3036,19 @@
         <v>11</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G10" s="14" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H10" s="21" t="s">
         <v>8</v>
@@ -3054,7 +3057,7 @@
         <v>61</v>
       </c>
       <c r="J10" s="14" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="11" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -3065,19 +3068,19 @@
         <v>11</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D11" s="18" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E11" s="18" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F11" s="18" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G11" s="18" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H11" s="21" t="s">
         <v>8</v>
@@ -3086,7 +3089,7 @@
         <v>61</v>
       </c>
       <c r="J11" s="18" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="12" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -3097,19 +3100,19 @@
         <v>14</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G12" s="14" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H12" s="16" t="s">
         <v>6</v>
@@ -3118,7 +3121,7 @@
         <v>61</v>
       </c>
       <c r="J12" s="14" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="13" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -3129,19 +3132,19 @@
         <v>14</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D13" s="18" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E13" s="18" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F13" s="18" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G13" s="18" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H13" s="20" t="s">
         <v>7</v>
@@ -3150,7 +3153,7 @@
         <v>61</v>
       </c>
       <c r="J13" s="18" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -3161,19 +3164,19 @@
         <v>14</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F14" s="14" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G14" s="14" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H14" s="16" t="s">
         <v>6</v>
@@ -3182,7 +3185,7 @@
         <v>61</v>
       </c>
       <c r="J14" s="14" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -3193,19 +3196,19 @@
         <v>14</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D15" s="18" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E15" s="18" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F15" s="18" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G15" s="18" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H15" s="20" t="s">
         <v>7</v>
@@ -3214,7 +3217,7 @@
         <v>61</v>
       </c>
       <c r="J15" s="18" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="16" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -3225,19 +3228,19 @@
         <v>14</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F16" s="14" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G16" s="14" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H16" s="21" t="s">
         <v>8</v>
@@ -3246,7 +3249,7 @@
         <v>61</v>
       </c>
       <c r="J16" s="14" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="17" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -3257,28 +3260,28 @@
         <v>14</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D17" s="18" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E17" s="18" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F17" s="18" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G17" s="18" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H17" s="20" t="s">
         <v>7</v>
       </c>
       <c r="I17" s="17" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="J17" s="18" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="18" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -3289,19 +3292,19 @@
         <v>14</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F18" s="14" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G18" s="14" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H18" s="20" t="s">
         <v>7</v>
@@ -3310,7 +3313,7 @@
         <v>61</v>
       </c>
       <c r="J18" s="14" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="19" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -3321,19 +3324,19 @@
         <v>14</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D19" s="18" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E19" s="18" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F19" s="18" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G19" s="18" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H19" s="21" t="s">
         <v>8</v>
@@ -3342,7 +3345,7 @@
         <v>61</v>
       </c>
       <c r="J19" s="18" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="20" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -3353,19 +3356,19 @@
         <v>14</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F20" s="14" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G20" s="14" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H20" s="20" t="s">
         <v>7</v>
@@ -3374,7 +3377,7 @@
         <v>61</v>
       </c>
       <c r="J20" s="14" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="21" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -3385,19 +3388,19 @@
         <v>16</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D21" s="18" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E21" s="18" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F21" s="18" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="G21" s="18" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H21" s="16" t="s">
         <v>6</v>
@@ -3406,7 +3409,7 @@
         <v>61</v>
       </c>
       <c r="J21" s="18" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="22" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -3417,19 +3420,19 @@
         <v>16</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F22" s="14" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G22" s="14" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H22" s="16" t="s">
         <v>6</v>
@@ -3438,7 +3441,7 @@
         <v>61</v>
       </c>
       <c r="J22" s="14" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="23" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -3449,19 +3452,19 @@
         <v>16</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D23" s="18" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E23" s="18" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F23" s="18" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G23" s="18" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H23" s="16" t="s">
         <v>6</v>
@@ -3470,7 +3473,7 @@
         <v>61</v>
       </c>
       <c r="J23" s="18" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="24" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -3481,19 +3484,19 @@
         <v>16</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D24" s="14" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F24" s="14" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G24" s="14" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H24" s="21" t="s">
         <v>8</v>
@@ -3502,7 +3505,7 @@
         <v>61</v>
       </c>
       <c r="J24" s="14" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="25" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -3513,28 +3516,28 @@
         <v>16</v>
       </c>
       <c r="C25" s="19" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D25" s="18" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E25" s="18" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F25" s="18" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G25" s="18" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H25" s="16" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I25" s="17" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="J25" s="18" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="26" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -3545,28 +3548,28 @@
         <v>16</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D26" s="14" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F26" s="14" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G26" s="14" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H26" s="16" t="s">
         <v>6</v>
       </c>
       <c r="I26" s="17" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="J26" s="14" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="27" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -3577,19 +3580,19 @@
         <v>18</v>
       </c>
       <c r="C27" s="19" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D27" s="18" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E27" s="18" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F27" s="18" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G27" s="18" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H27" s="16" t="s">
         <v>6</v>
@@ -3598,7 +3601,7 @@
         <v>61</v>
       </c>
       <c r="J27" s="18" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="28" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -3609,19 +3612,19 @@
         <v>18</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E28" s="14" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F28" s="14" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G28" s="14" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H28" s="20" t="s">
         <v>7</v>
@@ -3630,7 +3633,7 @@
         <v>61</v>
       </c>
       <c r="J28" s="14" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="29" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -3641,19 +3644,19 @@
         <v>18</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D29" s="18" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E29" s="18" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F29" s="18" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G29" s="18" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H29" s="16" t="s">
         <v>6</v>
@@ -3662,7 +3665,7 @@
         <v>61</v>
       </c>
       <c r="J29" s="18" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="30" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -3673,19 +3676,19 @@
         <v>18</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D30" s="14" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E30" s="14" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F30" s="14" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="G30" s="14" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H30" s="20" t="s">
         <v>7</v>
@@ -3694,7 +3697,7 @@
         <v>61</v>
       </c>
       <c r="J30" s="14" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="31" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -3705,19 +3708,19 @@
         <v>18</v>
       </c>
       <c r="C31" s="19" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D31" s="18" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E31" s="18" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F31" s="18" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="G31" s="18" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H31" s="20" t="s">
         <v>7</v>
@@ -3726,7 +3729,7 @@
         <v>61</v>
       </c>
       <c r="J31" s="18" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="32" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -3737,19 +3740,19 @@
         <v>18</v>
       </c>
       <c r="C32" s="15" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D32" s="14" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E32" s="14" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F32" s="14" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="G32" s="14" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H32" s="16" t="s">
         <v>6</v>
@@ -3758,7 +3761,7 @@
         <v>61</v>
       </c>
       <c r="J32" s="14" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="33" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -3769,19 +3772,19 @@
         <v>18</v>
       </c>
       <c r="C33" s="19" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D33" s="18" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E33" s="18" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F33" s="18" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G33" s="18" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H33" s="16" t="s">
         <v>6</v>
@@ -3790,7 +3793,7 @@
         <v>61</v>
       </c>
       <c r="J33" s="18" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="34" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -3801,19 +3804,19 @@
         <v>18</v>
       </c>
       <c r="C34" s="15" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D34" s="14" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E34" s="14" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F34" s="14" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="G34" s="14" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H34" s="21" t="s">
         <v>8</v>
@@ -3822,7 +3825,7 @@
         <v>61</v>
       </c>
       <c r="J34" s="14" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="35" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -3833,19 +3836,19 @@
         <v>18</v>
       </c>
       <c r="C35" s="19" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D35" s="18" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E35" s="18" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F35" s="18" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="G35" s="18" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H35" s="20" t="s">
         <v>7</v>
@@ -3854,7 +3857,7 @@
         <v>61</v>
       </c>
       <c r="J35" s="18" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="36" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -3865,19 +3868,19 @@
         <v>18</v>
       </c>
       <c r="C36" s="15" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D36" s="14" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E36" s="14" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F36" s="14" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="G36" s="14" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H36" s="20" t="s">
         <v>7</v>
@@ -3886,7 +3889,7 @@
         <v>61</v>
       </c>
       <c r="J36" s="14" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="37" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -3897,19 +3900,19 @@
         <v>18</v>
       </c>
       <c r="C37" s="19" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D37" s="18" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E37" s="18" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F37" s="18" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="G37" s="18" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H37" s="20" t="s">
         <v>7</v>
@@ -3918,7 +3921,7 @@
         <v>61</v>
       </c>
       <c r="J37" s="18" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="38" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -3929,19 +3932,19 @@
         <v>20</v>
       </c>
       <c r="C38" s="15" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D38" s="14" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E38" s="14" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F38" s="14" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="G38" s="14" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H38" s="16" t="s">
         <v>6</v>
@@ -3950,7 +3953,7 @@
         <v>61</v>
       </c>
       <c r="J38" s="14" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="39" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -3961,19 +3964,19 @@
         <v>20</v>
       </c>
       <c r="C39" s="19" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D39" s="18" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E39" s="18" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F39" s="18" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="G39" s="18" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H39" s="16" t="s">
         <v>6</v>
@@ -3982,7 +3985,7 @@
         <v>61</v>
       </c>
       <c r="J39" s="18" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="40" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -3993,19 +3996,19 @@
         <v>20</v>
       </c>
       <c r="C40" s="15" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D40" s="14" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E40" s="14" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F40" s="14" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="G40" s="14" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H40" s="20" t="s">
         <v>7</v>
@@ -4014,7 +4017,7 @@
         <v>61</v>
       </c>
       <c r="J40" s="14" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="41" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -4025,19 +4028,19 @@
         <v>20</v>
       </c>
       <c r="C41" s="19" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D41" s="18" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E41" s="18" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F41" s="18" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="G41" s="18" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H41" s="21" t="s">
         <v>8</v>
@@ -4046,7 +4049,7 @@
         <v>61</v>
       </c>
       <c r="J41" s="18" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="42" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -4057,19 +4060,19 @@
         <v>20</v>
       </c>
       <c r="C42" s="15" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D42" s="14" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E42" s="14" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F42" s="14" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="G42" s="14" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H42" s="21" t="s">
         <v>8</v>
@@ -4078,7 +4081,7 @@
         <v>61</v>
       </c>
       <c r="J42" s="14" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="43" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -4089,19 +4092,19 @@
         <v>22</v>
       </c>
       <c r="C43" s="19" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D43" s="18" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E43" s="18" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F43" s="18" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="G43" s="18" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H43" s="16" t="s">
         <v>6</v>
@@ -4110,7 +4113,7 @@
         <v>61</v>
       </c>
       <c r="J43" s="18" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="44" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -4121,19 +4124,19 @@
         <v>22</v>
       </c>
       <c r="C44" s="15" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D44" s="14" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E44" s="14" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F44" s="14" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="G44" s="14" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H44" s="16" t="s">
         <v>6</v>
@@ -4142,7 +4145,7 @@
         <v>61</v>
       </c>
       <c r="J44" s="14" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="45" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -4153,19 +4156,19 @@
         <v>22</v>
       </c>
       <c r="C45" s="19" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D45" s="18" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E45" s="18" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F45" s="18" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="G45" s="18" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H45" s="20" t="s">
         <v>7</v>
@@ -4174,7 +4177,7 @@
         <v>61</v>
       </c>
       <c r="J45" s="18" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="46" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -4185,19 +4188,19 @@
         <v>22</v>
       </c>
       <c r="C46" s="15" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D46" s="14" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E46" s="14" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F46" s="14" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="G46" s="14" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H46" s="21" t="s">
         <v>8</v>
@@ -4206,7 +4209,7 @@
         <v>61</v>
       </c>
       <c r="J46" s="14" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="47" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -4217,19 +4220,19 @@
         <v>22</v>
       </c>
       <c r="C47" s="19" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D47" s="18" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E47" s="18" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F47" s="18" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="G47" s="18" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H47" s="20" t="s">
         <v>7</v>
@@ -4238,7 +4241,7 @@
         <v>61</v>
       </c>
       <c r="J47" s="18" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="48" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -4249,19 +4252,19 @@
         <v>22</v>
       </c>
       <c r="C48" s="15" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D48" s="14" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E48" s="14" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F48" s="14" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="G48" s="14" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H48" s="20" t="s">
         <v>7</v>
@@ -4270,7 +4273,7 @@
         <v>61</v>
       </c>
       <c r="J48" s="14" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="49" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -4281,19 +4284,19 @@
         <v>22</v>
       </c>
       <c r="C49" s="19" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D49" s="18" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E49" s="18" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F49" s="18" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="G49" s="18" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H49" s="16" t="s">
         <v>6</v>
@@ -4302,7 +4305,7 @@
         <v>61</v>
       </c>
       <c r="J49" s="18" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="50" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -4313,28 +4316,28 @@
         <v>24</v>
       </c>
       <c r="C50" s="15" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D50" s="14" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="E50" s="14" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F50" s="14" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="G50" s="14" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H50" s="16" t="s">
         <v>6</v>
       </c>
       <c r="I50" s="17" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="J50" s="14" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="51" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -4345,28 +4348,28 @@
         <v>24</v>
       </c>
       <c r="C51" s="19" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D51" s="18" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E51" s="18" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F51" s="18" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="G51" s="18" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H51" s="16" t="s">
         <v>6</v>
       </c>
       <c r="I51" s="17" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="J51" s="18" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="52" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -4377,28 +4380,28 @@
         <v>24</v>
       </c>
       <c r="C52" s="15" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D52" s="14" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E52" s="14" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F52" s="14" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="G52" s="14" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H52" s="20" t="s">
         <v>7</v>
       </c>
       <c r="I52" s="17" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="J52" s="14" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="53" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -4409,28 +4412,28 @@
         <v>24</v>
       </c>
       <c r="C53" s="19" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D53" s="18" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E53" s="18" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F53" s="18" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="G53" s="18" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H53" s="21" t="s">
         <v>8</v>
       </c>
       <c r="I53" s="17" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="J53" s="18" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="54" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -4441,19 +4444,19 @@
         <v>24</v>
       </c>
       <c r="C54" s="15" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D54" s="14" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E54" s="14" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F54" s="14" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="G54" s="14" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H54" s="20" t="s">
         <v>7</v>
@@ -4462,7 +4465,7 @@
         <v>61</v>
       </c>
       <c r="J54" s="14" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="55" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -4473,19 +4476,19 @@
         <v>24</v>
       </c>
       <c r="C55" s="19" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D55" s="18" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E55" s="18" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F55" s="18" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="G55" s="18" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H55" s="21" t="s">
         <v>8</v>
@@ -4494,7 +4497,7 @@
         <v>61</v>
       </c>
       <c r="J55" s="18" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="56" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -4505,19 +4508,19 @@
         <v>24</v>
       </c>
       <c r="C56" s="15" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D56" s="14" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E56" s="14" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F56" s="14" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="G56" s="14" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H56" s="21" t="s">
         <v>8</v>
@@ -4526,7 +4529,7 @@
         <v>61</v>
       </c>
       <c r="J56" s="14" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="57" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -4537,28 +4540,28 @@
         <v>26</v>
       </c>
       <c r="C57" s="19" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D57" s="18" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E57" s="18" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F57" s="18" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G57" s="18" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H57" s="16" t="s">
         <v>6</v>
       </c>
       <c r="I57" s="17" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="J57" s="18" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="58" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -4569,28 +4572,28 @@
         <v>26</v>
       </c>
       <c r="C58" s="15" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D58" s="14" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E58" s="14" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F58" s="14" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="G58" s="14" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H58" s="16" t="s">
         <v>6</v>
       </c>
       <c r="I58" s="17" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="J58" s="14" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="59" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -4601,19 +4604,19 @@
         <v>26</v>
       </c>
       <c r="C59" s="19" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D59" s="18" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E59" s="18" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F59" s="18" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="G59" s="18" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H59" s="20" t="s">
         <v>7</v>
@@ -4622,7 +4625,7 @@
         <v>61</v>
       </c>
       <c r="J59" s="18" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="60" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -4633,28 +4636,28 @@
         <v>26</v>
       </c>
       <c r="C60" s="15" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D60" s="14" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E60" s="14" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F60" s="14" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="G60" s="14" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H60" s="16" t="s">
         <v>6</v>
       </c>
       <c r="I60" s="17" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="J60" s="14" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="61" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -4665,19 +4668,19 @@
         <v>26</v>
       </c>
       <c r="C61" s="19" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D61" s="18" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E61" s="18" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="F61" s="18" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="G61" s="18" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H61" s="20" t="s">
         <v>7</v>
@@ -4686,7 +4689,7 @@
         <v>61</v>
       </c>
       <c r="J61" s="18" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="62" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -4697,19 +4700,19 @@
         <v>26</v>
       </c>
       <c r="C62" s="15" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D62" s="14" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="E62" s="14" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F62" s="14" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="G62" s="14" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H62" s="21" t="s">
         <v>8</v>
@@ -4718,7 +4721,7 @@
         <v>61</v>
       </c>
       <c r="J62" s="14" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="63" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -4729,28 +4732,28 @@
         <v>28</v>
       </c>
       <c r="C63" s="19" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D63" s="18" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E63" s="18" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="F63" s="18" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="G63" s="18" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H63" s="16" t="s">
         <v>6</v>
       </c>
       <c r="I63" s="17" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="J63" s="18" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="64" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -4761,28 +4764,28 @@
         <v>28</v>
       </c>
       <c r="C64" s="15" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D64" s="14" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E64" s="14" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="F64" s="14" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="G64" s="14" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H64" s="20" t="s">
         <v>7</v>
       </c>
       <c r="I64" s="17" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="J64" s="14" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="65" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -4793,19 +4796,19 @@
         <v>28</v>
       </c>
       <c r="C65" s="19" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D65" s="18" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E65" s="18" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F65" s="18" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="G65" s="18" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H65" s="20" t="s">
         <v>7</v>
@@ -4814,7 +4817,7 @@
         <v>61</v>
       </c>
       <c r="J65" s="18" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="66" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -4825,19 +4828,19 @@
         <v>28</v>
       </c>
       <c r="C66" s="15" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D66" s="14" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E66" s="14" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F66" s="14" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="G66" s="14" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H66" s="21" t="s">
         <v>8</v>
@@ -4846,7 +4849,7 @@
         <v>61</v>
       </c>
       <c r="J66" s="14" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="67" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -4857,19 +4860,19 @@
         <v>30</v>
       </c>
       <c r="C67" s="19" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D67" s="18" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E67" s="18" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="F67" s="18" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="G67" s="18" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H67" s="20" t="s">
         <v>7</v>
@@ -4878,7 +4881,7 @@
         <v>61</v>
       </c>
       <c r="J67" s="18" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="68" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -4889,19 +4892,19 @@
         <v>30</v>
       </c>
       <c r="C68" s="15" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D68" s="14" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E68" s="14" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="F68" s="14" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="G68" s="14" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H68" s="20" t="s">
         <v>7</v>
@@ -4910,7 +4913,7 @@
         <v>61</v>
       </c>
       <c r="J68" s="14" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="69" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -4921,19 +4924,19 @@
         <v>30</v>
       </c>
       <c r="C69" s="19" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D69" s="18" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="E69" s="18" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="F69" s="18" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="G69" s="18" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H69" s="20" t="s">
         <v>7</v>
@@ -4942,7 +4945,7 @@
         <v>61</v>
       </c>
       <c r="J69" s="18" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="70" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -4953,19 +4956,19 @@
         <v>30</v>
       </c>
       <c r="C70" s="15" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D70" s="14" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="E70" s="14" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="F70" s="14" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="G70" s="14" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H70" s="20" t="s">
         <v>7</v>
@@ -4974,7 +4977,7 @@
         <v>61</v>
       </c>
       <c r="J70" s="14" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="71" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -4985,19 +4988,19 @@
         <v>30</v>
       </c>
       <c r="C71" s="19" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D71" s="18" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="E71" s="18" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F71" s="18" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="G71" s="18" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H71" s="20" t="s">
         <v>7</v>
@@ -5006,7 +5009,7 @@
         <v>61</v>
       </c>
       <c r="J71" s="18" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="72" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -5017,19 +5020,19 @@
         <v>30</v>
       </c>
       <c r="C72" s="15" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D72" s="14" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E72" s="14" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="F72" s="14" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="G72" s="14" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H72" s="21" t="s">
         <v>8</v>
@@ -5038,7 +5041,7 @@
         <v>61</v>
       </c>
       <c r="J72" s="14" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="73" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -5049,19 +5052,19 @@
         <v>30</v>
       </c>
       <c r="C73" s="19" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D73" s="18" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E73" s="18" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="F73" s="18" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="G73" s="18" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H73" s="20" t="s">
         <v>7</v>
@@ -5070,7 +5073,7 @@
         <v>61</v>
       </c>
       <c r="J73" s="18" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="74" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -5081,19 +5084,19 @@
         <v>30</v>
       </c>
       <c r="C74" s="15" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D74" s="14" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E74" s="14" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F74" s="14" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="G74" s="14" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H74" s="16" t="s">
         <v>6</v>
@@ -5102,7 +5105,7 @@
         <v>61</v>
       </c>
       <c r="J74" s="14" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="75" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -5113,19 +5116,19 @@
         <v>30</v>
       </c>
       <c r="C75" s="19" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D75" s="18" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="E75" s="18" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="F75" s="18" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="G75" s="18" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H75" s="21" t="s">
         <v>8</v>
@@ -5134,7 +5137,7 @@
         <v>61</v>
       </c>
       <c r="J75" s="18" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="76" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -5145,19 +5148,19 @@
         <v>32</v>
       </c>
       <c r="C76" s="15" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D76" s="14" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="E76" s="14" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="F76" s="14" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="G76" s="14" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H76" s="16" t="s">
         <v>6</v>
@@ -5166,7 +5169,7 @@
         <v>61</v>
       </c>
       <c r="J76" s="14" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="77" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -5177,19 +5180,19 @@
         <v>32</v>
       </c>
       <c r="C77" s="19" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="D77" s="18" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="E77" s="18" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="F77" s="18" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="G77" s="18" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H77" s="16" t="s">
         <v>6</v>
@@ -5198,7 +5201,7 @@
         <v>61</v>
       </c>
       <c r="J77" s="18" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="78" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -5209,19 +5212,19 @@
         <v>32</v>
       </c>
       <c r="C78" s="15" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="D78" s="14" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="E78" s="14" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="F78" s="14" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="G78" s="14" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H78" s="16" t="s">
         <v>6</v>
@@ -5230,7 +5233,7 @@
         <v>61</v>
       </c>
       <c r="J78" s="14" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="79" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -5241,19 +5244,19 @@
         <v>32</v>
       </c>
       <c r="C79" s="19" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="D79" s="18" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="E79" s="18" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="F79" s="18" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="G79" s="18" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H79" s="21" t="s">
         <v>8</v>
@@ -5262,7 +5265,7 @@
         <v>61</v>
       </c>
       <c r="J79" s="18" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="80" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -5273,19 +5276,19 @@
         <v>32</v>
       </c>
       <c r="C80" s="15" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="D80" s="14" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="E80" s="14" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="F80" s="14" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="G80" s="14" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H80" s="20" t="s">
         <v>7</v>
@@ -5294,7 +5297,7 @@
         <v>61</v>
       </c>
       <c r="J80" s="14" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="81" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -5305,19 +5308,19 @@
         <v>32</v>
       </c>
       <c r="C81" s="19" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="D81" s="18" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="E81" s="18" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F81" s="18" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="G81" s="18" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H81" s="20" t="s">
         <v>7</v>
@@ -5326,7 +5329,7 @@
         <v>61</v>
       </c>
       <c r="J81" s="18" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
   </sheetData>
@@ -5441,10 +5444,10 @@
         <v>6</v>
       </c>
       <c r="I3" s="17" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="J3" s="14" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -5455,28 +5458,28 @@
         <v>11</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H4" s="16" t="s">
         <v>6</v>
       </c>
       <c r="I4" s="17" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="J4" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -5487,28 +5490,28 @@
         <v>11</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F5" s="14" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G5" s="14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H5" s="16" t="s">
         <v>6</v>
       </c>
       <c r="I5" s="17" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="J5" s="14" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -5519,28 +5522,28 @@
         <v>11</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F6" s="14" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G6" s="14" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H6" s="16" t="s">
         <v>6</v>
       </c>
       <c r="I6" s="17" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="J6" s="14" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -5551,19 +5554,19 @@
         <v>11</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H7" s="20" t="s">
         <v>7</v>
@@ -5572,7 +5575,7 @@
         <v>61</v>
       </c>
       <c r="J7" s="14" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="8" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -5583,19 +5586,19 @@
         <v>11</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F8" s="14" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G8" s="14" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H8" s="20" t="s">
         <v>7</v>
@@ -5604,7 +5607,7 @@
         <v>61</v>
       </c>
       <c r="J8" s="14" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -5615,19 +5618,19 @@
         <v>11</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H9" s="16" t="s">
         <v>6</v>
@@ -5636,7 +5639,7 @@
         <v>61</v>
       </c>
       <c r="J9" s="14" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="10" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -5647,19 +5650,19 @@
         <v>11</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G10" s="14" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H10" s="21" t="s">
         <v>8</v>
@@ -5668,7 +5671,7 @@
         <v>61</v>
       </c>
       <c r="J10" s="14" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="11" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -5679,19 +5682,19 @@
         <v>11</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G11" s="14" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H11" s="21" t="s">
         <v>8</v>
@@ -5700,7 +5703,7 @@
         <v>61</v>
       </c>
       <c r="J11" s="14" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="12" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -5711,19 +5714,19 @@
         <v>14</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G12" s="14" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H12" s="16" t="s">
         <v>6</v>
@@ -5732,7 +5735,7 @@
         <v>61</v>
       </c>
       <c r="J12" s="14" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="13" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -5743,19 +5746,19 @@
         <v>14</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F13" s="14" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G13" s="14" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H13" s="20" t="s">
         <v>7</v>
@@ -5764,7 +5767,7 @@
         <v>61</v>
       </c>
       <c r="J13" s="14" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -5775,19 +5778,19 @@
         <v>14</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F14" s="14" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G14" s="14" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H14" s="16" t="s">
         <v>6</v>
@@ -5796,7 +5799,7 @@
         <v>61</v>
       </c>
       <c r="J14" s="14" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -5807,19 +5810,19 @@
         <v>14</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F15" s="14" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G15" s="14" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H15" s="20" t="s">
         <v>7</v>
@@ -5828,7 +5831,7 @@
         <v>61</v>
       </c>
       <c r="J15" s="14" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="16" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -5839,19 +5842,19 @@
         <v>14</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F16" s="14" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G16" s="14" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H16" s="21" t="s">
         <v>8</v>
@@ -5860,7 +5863,7 @@
         <v>61</v>
       </c>
       <c r="J16" s="14" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="17" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -5871,28 +5874,28 @@
         <v>14</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F17" s="14" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G17" s="14" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H17" s="20" t="s">
         <v>7</v>
       </c>
       <c r="I17" s="17" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="J17" s="14" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="18" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -5903,19 +5906,19 @@
         <v>14</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F18" s="14" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G18" s="14" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H18" s="20" t="s">
         <v>7</v>
@@ -5924,7 +5927,7 @@
         <v>61</v>
       </c>
       <c r="J18" s="14" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="19" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -5935,19 +5938,19 @@
         <v>14</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F19" s="14" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G19" s="14" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H19" s="21" t="s">
         <v>8</v>
@@ -5956,7 +5959,7 @@
         <v>61</v>
       </c>
       <c r="J19" s="14" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="20" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -5967,19 +5970,19 @@
         <v>14</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F20" s="14" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G20" s="14" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H20" s="20" t="s">
         <v>7</v>
@@ -5988,7 +5991,7 @@
         <v>61</v>
       </c>
       <c r="J20" s="14" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="21" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -5999,19 +6002,19 @@
         <v>16</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F21" s="14" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="G21" s="14" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H21" s="16" t="s">
         <v>6</v>
@@ -6020,7 +6023,7 @@
         <v>61</v>
       </c>
       <c r="J21" s="14" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="22" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -6031,19 +6034,19 @@
         <v>16</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F22" s="14" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G22" s="14" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H22" s="16" t="s">
         <v>6</v>
@@ -6052,7 +6055,7 @@
         <v>61</v>
       </c>
       <c r="J22" s="14" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="23" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -6063,19 +6066,19 @@
         <v>16</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D23" s="14" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F23" s="14" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G23" s="14" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H23" s="16" t="s">
         <v>6</v>
@@ -6084,7 +6087,7 @@
         <v>61</v>
       </c>
       <c r="J23" s="14" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="24" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -6095,19 +6098,19 @@
         <v>16</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D24" s="14" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F24" s="14" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G24" s="14" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H24" s="21" t="s">
         <v>8</v>
@@ -6116,7 +6119,7 @@
         <v>61</v>
       </c>
       <c r="J24" s="14" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="25" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -6127,28 +6130,28 @@
         <v>16</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D25" s="14" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E25" s="14" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F25" s="14" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G25" s="14" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H25" s="16" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I25" s="17" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="J25" s="14" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="26" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -6159,28 +6162,28 @@
         <v>16</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D26" s="14" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F26" s="14" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G26" s="14" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H26" s="16" t="s">
         <v>6</v>
       </c>
       <c r="I26" s="17" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="J26" s="14" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="27" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -6191,19 +6194,19 @@
         <v>18</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D27" s="14" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E27" s="14" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F27" s="14" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G27" s="14" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H27" s="16" t="s">
         <v>6</v>
@@ -6212,7 +6215,7 @@
         <v>61</v>
       </c>
       <c r="J27" s="14" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="28" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -6223,19 +6226,19 @@
         <v>18</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E28" s="14" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F28" s="14" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G28" s="14" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H28" s="20" t="s">
         <v>7</v>
@@ -6244,7 +6247,7 @@
         <v>61</v>
       </c>
       <c r="J28" s="14" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="29" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -6255,19 +6258,19 @@
         <v>18</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D29" s="14" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E29" s="14" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F29" s="14" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G29" s="14" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H29" s="16" t="s">
         <v>6</v>
@@ -6276,7 +6279,7 @@
         <v>61</v>
       </c>
       <c r="J29" s="14" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="30" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -6287,19 +6290,19 @@
         <v>18</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D30" s="14" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E30" s="14" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F30" s="14" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="G30" s="14" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H30" s="20" t="s">
         <v>7</v>
@@ -6308,7 +6311,7 @@
         <v>61</v>
       </c>
       <c r="J30" s="14" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="31" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -6319,19 +6322,19 @@
         <v>18</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D31" s="14" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E31" s="14" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F31" s="14" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="G31" s="14" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H31" s="20" t="s">
         <v>7</v>
@@ -6340,7 +6343,7 @@
         <v>61</v>
       </c>
       <c r="J31" s="14" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="32" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -6351,19 +6354,19 @@
         <v>18</v>
       </c>
       <c r="C32" s="15" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D32" s="14" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E32" s="14" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F32" s="14" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="G32" s="14" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H32" s="16" t="s">
         <v>6</v>
@@ -6372,7 +6375,7 @@
         <v>61</v>
       </c>
       <c r="J32" s="14" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="33" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -6383,19 +6386,19 @@
         <v>18</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D33" s="14" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E33" s="14" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F33" s="14" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G33" s="14" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H33" s="16" t="s">
         <v>6</v>
@@ -6404,7 +6407,7 @@
         <v>61</v>
       </c>
       <c r="J33" s="14" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="34" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -6415,19 +6418,19 @@
         <v>18</v>
       </c>
       <c r="C34" s="15" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D34" s="14" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E34" s="14" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F34" s="14" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="G34" s="14" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H34" s="21" t="s">
         <v>8</v>
@@ -6436,7 +6439,7 @@
         <v>61</v>
       </c>
       <c r="J34" s="14" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="35" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -6447,19 +6450,19 @@
         <v>18</v>
       </c>
       <c r="C35" s="15" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D35" s="14" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E35" s="14" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F35" s="14" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="G35" s="14" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H35" s="20" t="s">
         <v>7</v>
@@ -6468,7 +6471,7 @@
         <v>61</v>
       </c>
       <c r="J35" s="14" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="36" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -6479,19 +6482,19 @@
         <v>18</v>
       </c>
       <c r="C36" s="15" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D36" s="14" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E36" s="14" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F36" s="14" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="G36" s="14" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H36" s="20" t="s">
         <v>7</v>
@@ -6500,7 +6503,7 @@
         <v>61</v>
       </c>
       <c r="J36" s="14" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="37" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -6511,19 +6514,19 @@
         <v>18</v>
       </c>
       <c r="C37" s="15" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D37" s="14" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E37" s="14" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F37" s="14" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="G37" s="14" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H37" s="20" t="s">
         <v>7</v>
@@ -6532,7 +6535,7 @@
         <v>61</v>
       </c>
       <c r="J37" s="14" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="38" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -6543,19 +6546,19 @@
         <v>20</v>
       </c>
       <c r="C38" s="15" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D38" s="14" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E38" s="14" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F38" s="14" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="G38" s="14" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H38" s="16" t="s">
         <v>6</v>
@@ -6564,7 +6567,7 @@
         <v>61</v>
       </c>
       <c r="J38" s="14" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="39" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -6575,19 +6578,19 @@
         <v>20</v>
       </c>
       <c r="C39" s="15" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D39" s="14" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E39" s="14" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F39" s="14" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="G39" s="14" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H39" s="16" t="s">
         <v>6</v>
@@ -6596,7 +6599,7 @@
         <v>61</v>
       </c>
       <c r="J39" s="14" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="40" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -6607,19 +6610,19 @@
         <v>20</v>
       </c>
       <c r="C40" s="15" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D40" s="14" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E40" s="14" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F40" s="14" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="G40" s="14" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H40" s="20" t="s">
         <v>7</v>
@@ -6628,7 +6631,7 @@
         <v>61</v>
       </c>
       <c r="J40" s="14" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="41" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -6639,19 +6642,19 @@
         <v>20</v>
       </c>
       <c r="C41" s="15" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D41" s="14" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E41" s="14" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F41" s="14" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="G41" s="14" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H41" s="21" t="s">
         <v>8</v>
@@ -6660,7 +6663,7 @@
         <v>61</v>
       </c>
       <c r="J41" s="14" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="42" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -6671,19 +6674,19 @@
         <v>20</v>
       </c>
       <c r="C42" s="15" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D42" s="14" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E42" s="14" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F42" s="14" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="G42" s="14" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H42" s="21" t="s">
         <v>8</v>
@@ -6692,7 +6695,7 @@
         <v>61</v>
       </c>
       <c r="J42" s="14" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
   </sheetData>
@@ -6757,19 +6760,19 @@
         <v>22</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E2" s="14" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F2" s="14" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="G2" s="14" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H2" s="16" t="s">
         <v>6</v>
@@ -6778,7 +6781,7 @@
         <v>61</v>
       </c>
       <c r="J2" s="14" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -6789,19 +6792,19 @@
         <v>22</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F3" s="14" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="G3" s="14" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H3" s="16" t="s">
         <v>6</v>
@@ -6810,7 +6813,7 @@
         <v>61</v>
       </c>
       <c r="J3" s="14" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -6821,19 +6824,19 @@
         <v>22</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H4" s="20" t="s">
         <v>7</v>
@@ -6842,7 +6845,7 @@
         <v>61</v>
       </c>
       <c r="J4" s="14" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="5" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -6853,19 +6856,19 @@
         <v>22</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F5" s="14" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="G5" s="14" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H5" s="21" t="s">
         <v>8</v>
@@ -6874,7 +6877,7 @@
         <v>61</v>
       </c>
       <c r="J5" s="14" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="6" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -6885,19 +6888,19 @@
         <v>22</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F6" s="14" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="G6" s="14" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H6" s="20" t="s">
         <v>7</v>
@@ -6906,7 +6909,7 @@
         <v>61</v>
       </c>
       <c r="J6" s="14" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="7" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -6917,19 +6920,19 @@
         <v>22</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H7" s="20" t="s">
         <v>7</v>
@@ -6938,7 +6941,7 @@
         <v>61</v>
       </c>
       <c r="J7" s="14" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="8" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -6949,19 +6952,19 @@
         <v>22</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F8" s="14" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="G8" s="14" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H8" s="16" t="s">
         <v>6</v>
@@ -6970,7 +6973,7 @@
         <v>61</v>
       </c>
       <c r="J8" s="14" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
   </sheetData>
@@ -7035,28 +7038,28 @@
         <v>24</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="E2" s="14" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F2" s="14" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="G2" s="14" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H2" s="16" t="s">
         <v>6</v>
       </c>
       <c r="I2" s="17" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="J2" s="14" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -7067,28 +7070,28 @@
         <v>24</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F3" s="14" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="G3" s="14" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H3" s="16" t="s">
         <v>6</v>
       </c>
       <c r="I3" s="17" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="J3" s="14" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -7099,28 +7102,28 @@
         <v>24</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H4" s="20" t="s">
         <v>7</v>
       </c>
       <c r="I4" s="17" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="J4" s="14" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="5" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -7131,28 +7134,28 @@
         <v>24</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F5" s="14" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="G5" s="14" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H5" s="21" t="s">
         <v>8</v>
       </c>
       <c r="I5" s="17" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="J5" s="14" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="6" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -7163,19 +7166,19 @@
         <v>24</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F6" s="14" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="G6" s="14" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H6" s="20" t="s">
         <v>7</v>
@@ -7184,7 +7187,7 @@
         <v>61</v>
       </c>
       <c r="J6" s="14" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="7" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -7195,19 +7198,19 @@
         <v>24</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H7" s="21" t="s">
         <v>8</v>
@@ -7216,7 +7219,7 @@
         <v>61</v>
       </c>
       <c r="J7" s="14" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="8" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -7227,19 +7230,19 @@
         <v>24</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F8" s="14" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="G8" s="14" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H8" s="21" t="s">
         <v>8</v>
@@ -7248,7 +7251,7 @@
         <v>61</v>
       </c>
       <c r="J8" s="14" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
   </sheetData>
@@ -7313,28 +7316,28 @@
         <v>26</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E2" s="14" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F2" s="14" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G2" s="14" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H2" s="16" t="s">
         <v>6</v>
       </c>
       <c r="I2" s="17" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="J2" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -7345,28 +7348,28 @@
         <v>26</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F3" s="14" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="G3" s="14" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H3" s="16" t="s">
         <v>6</v>
       </c>
       <c r="I3" s="17" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="J3" s="14" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -7377,19 +7380,19 @@
         <v>26</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H4" s="20" t="s">
         <v>7</v>
@@ -7398,7 +7401,7 @@
         <v>61</v>
       </c>
       <c r="J4" s="14" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="5" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -7409,28 +7412,28 @@
         <v>26</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F5" s="14" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="G5" s="14" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H5" s="16" t="s">
         <v>6</v>
       </c>
       <c r="I5" s="17" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="J5" s="14" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="6" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -7441,19 +7444,19 @@
         <v>26</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="F6" s="14" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="G6" s="14" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H6" s="20" t="s">
         <v>7</v>
@@ -7462,7 +7465,7 @@
         <v>61</v>
       </c>
       <c r="J6" s="14" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="7" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -7473,19 +7476,19 @@
         <v>26</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H7" s="21" t="s">
         <v>8</v>
@@ -7494,7 +7497,7 @@
         <v>61</v>
       </c>
       <c r="J7" s="14" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
   </sheetData>
@@ -7559,28 +7562,28 @@
         <v>28</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E2" s="14" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="F2" s="14" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="G2" s="14" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H2" s="16" t="s">
         <v>6</v>
       </c>
       <c r="I2" s="17" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="J2" s="14" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -7591,28 +7594,28 @@
         <v>28</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="F3" s="14" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="G3" s="14" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H3" s="20" t="s">
         <v>7</v>
       </c>
       <c r="I3" s="17" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="J3" s="14" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -7623,19 +7626,19 @@
         <v>28</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H4" s="20" t="s">
         <v>7</v>
@@ -7644,7 +7647,7 @@
         <v>61</v>
       </c>
       <c r="J4" s="14" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="5" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -7655,19 +7658,19 @@
         <v>28</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F5" s="14" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="G5" s="14" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H5" s="21" t="s">
         <v>8</v>
@@ -7676,7 +7679,7 @@
         <v>61</v>
       </c>
       <c r="J5" s="14" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
   </sheetData>
@@ -7741,19 +7744,19 @@
         <v>30</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E2" s="14" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="F2" s="14" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="G2" s="14" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H2" s="20" t="s">
         <v>7</v>
@@ -7762,7 +7765,7 @@
         <v>61</v>
       </c>
       <c r="J2" s="14" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -7773,19 +7776,19 @@
         <v>30</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="F3" s="14" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="G3" s="14" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H3" s="20" t="s">
         <v>7</v>
@@ -7794,7 +7797,7 @@
         <v>61</v>
       </c>
       <c r="J3" s="14" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -7805,19 +7808,19 @@
         <v>30</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H4" s="20" t="s">
         <v>7</v>
@@ -7826,7 +7829,7 @@
         <v>61</v>
       </c>
       <c r="J4" s="14" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="5" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -7837,19 +7840,19 @@
         <v>30</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="F5" s="14" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="G5" s="14" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H5" s="20" t="s">
         <v>7</v>
@@ -7858,7 +7861,7 @@
         <v>61</v>
       </c>
       <c r="J5" s="14" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="6" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -7869,19 +7872,19 @@
         <v>30</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F6" s="14" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="G6" s="14" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H6" s="20" t="s">
         <v>7</v>
@@ -7890,7 +7893,7 @@
         <v>61</v>
       </c>
       <c r="J6" s="14" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="7" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -7901,19 +7904,19 @@
         <v>30</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H7" s="21" t="s">
         <v>8</v>
@@ -7922,7 +7925,7 @@
         <v>61</v>
       </c>
       <c r="J7" s="14" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="8" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -7933,19 +7936,19 @@
         <v>30</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="F8" s="14" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="G8" s="14" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H8" s="20" t="s">
         <v>7</v>
@@ -7954,7 +7957,7 @@
         <v>61</v>
       </c>
       <c r="J8" s="14" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="9" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -7965,19 +7968,19 @@
         <v>30</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H9" s="16" t="s">
         <v>6</v>
@@ -7986,7 +7989,7 @@
         <v>61</v>
       </c>
       <c r="J9" s="14" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="10" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -7997,19 +8000,19 @@
         <v>30</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="G10" s="14" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H10" s="21" t="s">
         <v>8</v>
@@ -8018,7 +8021,7 @@
         <v>61</v>
       </c>
       <c r="J10" s="14" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="11" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -8029,19 +8032,19 @@
         <v>32</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="G11" s="14" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H11" s="16" t="s">
         <v>6</v>
@@ -8050,7 +8053,7 @@
         <v>61</v>
       </c>
       <c r="J11" s="14" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="12" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -8061,19 +8064,19 @@
         <v>32</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="G12" s="14" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H12" s="16" t="s">
         <v>6</v>
@@ -8082,7 +8085,7 @@
         <v>61</v>
       </c>
       <c r="J12" s="14" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="13" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -8093,19 +8096,19 @@
         <v>32</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="F13" s="14" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="G13" s="14" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H13" s="16" t="s">
         <v>6</v>
@@ -8114,7 +8117,7 @@
         <v>61</v>
       </c>
       <c r="J13" s="14" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="14" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -8125,19 +8128,19 @@
         <v>32</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="F14" s="14" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="G14" s="14" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H14" s="21" t="s">
         <v>8</v>
@@ -8146,7 +8149,7 @@
         <v>61</v>
       </c>
       <c r="J14" s="14" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="15" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -8157,19 +8160,19 @@
         <v>32</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="F15" s="14" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="G15" s="14" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H15" s="20" t="s">
         <v>7</v>
@@ -8178,7 +8181,7 @@
         <v>61</v>
       </c>
       <c r="J15" s="14" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="16" spans="1:10" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -8189,19 +8192,19 @@
         <v>32</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F16" s="14" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="G16" s="14" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H16" s="20" t="s">
         <v>7</v>
@@ -8210,7 +8213,7 @@
         <v>61</v>
       </c>
       <c r="J16" s="14" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
   </sheetData>
